--- a/diseases/d170/2015-2019.xlsx
+++ b/diseases/d170/2015-2019.xlsx
@@ -776,6 +776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -924,6 +929,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1072,6 +1082,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1220,6 +1235,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1368,6 +1388,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1516,6 +1541,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1664,6 +1694,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1812,6 +1847,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1960,6 +2000,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2108,6 +2153,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2256,6 +2306,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2404,6 +2459,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2552,6 +2612,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2700,6 +2765,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2848,6 +2918,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2996,6 +3071,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3144,6 +3224,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3292,6 +3377,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3440,6 +3530,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3588,6 +3683,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3736,6 +3836,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3884,6 +3989,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4032,6 +4142,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4180,6 +4295,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4328,6 +4448,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4476,6 +4601,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4624,6 +4754,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4772,6 +4907,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4920,6 +5060,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5068,6 +5213,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5216,6 +5366,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5364,6 +5519,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5512,6 +5672,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5660,6 +5825,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5808,6 +5978,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5956,6 +6131,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6104,6 +6284,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6252,6 +6437,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6400,6 +6590,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6548,6 +6743,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6696,6 +6896,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6844,6 +7049,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6992,6 +7202,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7140,6 +7355,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7288,6 +7508,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7436,6 +7661,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7584,6 +7814,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7732,6 +7967,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7880,6 +8120,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8028,6 +8273,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8176,6 +8426,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8324,6 +8579,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8472,6 +8732,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8620,6 +8885,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8768,6 +9038,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8916,6 +9191,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9064,6 +9344,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9212,6 +9497,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9358,6 +9648,11 @@
       <c r="S60" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">

--- a/diseases/d170/2015-2019.xlsx
+++ b/diseases/d170/2015-2019.xlsx
@@ -771,11 +771,6 @@
       <c r="R2" t="n">
         <v>0.02125014248220534</v>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -788,22 +783,12 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
@@ -924,11 +909,6 @@
       <c r="R3" t="n">
         <v>0.03825025646796962</v>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -941,22 +921,12 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
@@ -1077,11 +1047,6 @@
       <c r="R4" t="n">
         <v>0.01700011398576427</v>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1094,22 +1059,12 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
@@ -1230,11 +1185,6 @@
       <c r="R5" t="n">
         <v>0.01700011398576427</v>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1247,22 +1197,12 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
@@ -1383,11 +1323,6 @@
       <c r="R6" t="n">
         <v>0.03400022797152855</v>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1400,22 +1335,12 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
@@ -1536,11 +1461,6 @@
       <c r="R7" t="n">
         <v>0.008500056992882137</v>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1553,22 +1473,12 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
@@ -1689,11 +1599,6 @@
       <c r="R8" t="n">
         <v>0.01700011398576427</v>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1706,22 +1611,12 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
@@ -1842,11 +1737,6 @@
       <c r="R9" t="n">
         <v>0.0127500854893232</v>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1859,22 +1749,12 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
@@ -1995,11 +1875,6 @@
       <c r="R10" t="n">
         <v>0.01700011398576427</v>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2012,22 +1887,12 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
@@ -2148,11 +2013,6 @@
       <c r="R11" t="n">
         <v>0.02975019947508748</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2165,22 +2025,12 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
@@ -2301,11 +2151,6 @@
       <c r="R12" t="n">
         <v>0.008500056992882137</v>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2318,22 +2163,12 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
@@ -2454,11 +2289,6 @@
       <c r="R13" t="n">
         <v>0.03400022797152855</v>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2471,22 +2301,12 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
@@ -2607,11 +2427,6 @@
       <c r="R14" t="n">
         <v>0.01271933297274024</v>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2624,22 +2439,12 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
@@ -2760,11 +2565,6 @@
       <c r="R15" t="n">
         <v>0.01695911063032032</v>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2777,22 +2577,12 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -2913,11 +2703,6 @@
       <c r="R16" t="n">
         <v>0.01271933297274024</v>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2930,22 +2715,12 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
@@ -3066,11 +2841,6 @@
       <c r="R17" t="n">
         <v>0.004239777657580081</v>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3083,22 +2853,12 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
@@ -3219,11 +2979,6 @@
       <c r="R18" t="n">
         <v>0.0211988882879004</v>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3236,22 +2991,12 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
-      </c>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
@@ -3372,11 +3117,6 @@
       <c r="R19" t="n">
         <v>0.01271933297274024</v>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3389,22 +3129,12 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
-      </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
@@ -3525,11 +3255,6 @@
       <c r="R20" t="n">
         <v>0.01695911063032032</v>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3542,22 +3267,12 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
-      </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
@@ -3678,11 +3393,6 @@
       <c r="R21" t="n">
         <v>0.01271933297274024</v>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3695,22 +3405,12 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
-      </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
@@ -3831,11 +3531,6 @@
       <c r="R22" t="n">
         <v>0.01271933297274024</v>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3848,22 +3543,12 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
         <v>0</v>
-      </c>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
@@ -3984,11 +3669,6 @@
       <c r="R23" t="n">
         <v>0.02967844360306057</v>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4001,22 +3681,12 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
         <v>0</v>
-      </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
@@ -4137,11 +3807,6 @@
       <c r="R24" t="n">
         <v>0.008479555315160162</v>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4154,22 +3819,12 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR24" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
         <v>0</v>
-      </c>
-      <c r="AU24" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
@@ -4290,11 +3945,6 @@
       <c r="R25" t="n">
         <v>0.008479555315160162</v>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4307,22 +3957,12 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR25" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
         <v>0</v>
-      </c>
-      <c r="AU25" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
@@ -4443,11 +4083,6 @@
       <c r="R26" t="n">
         <v>0.004231380697829149</v>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4460,22 +4095,12 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR26" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
         <v>0</v>
-      </c>
-      <c r="AU26" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
@@ -4596,11 +4221,6 @@
       <c r="R27" t="n">
         <v>0.004231380697829149</v>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4613,22 +4233,12 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR27" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
         <v>0</v>
-      </c>
-      <c r="AU27" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
@@ -4749,11 +4359,6 @@
       <c r="R28" t="n">
         <v>0.01269414209348745</v>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4766,22 +4371,12 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR28" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="n">
         <v>0</v>
-      </c>
-      <c r="AU28" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
@@ -4902,11 +4497,6 @@
       <c r="R29" t="n">
         <v>0.01269414209348745</v>
       </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4919,22 +4509,12 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR29" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
         <v>0</v>
-      </c>
-      <c r="AU29" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
@@ -5055,11 +4635,6 @@
       <c r="R30" t="n">
         <v>0.01269414209348745</v>
       </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5072,22 +4647,12 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR30" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="n">
         <v>0</v>
-      </c>
-      <c r="AU30" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
@@ -5208,11 +4773,6 @@
       <c r="R31" t="n">
         <v>0.02115690348914575</v>
       </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5225,22 +4785,12 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR31" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
         <v>0</v>
-      </c>
-      <c r="AU31" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
@@ -5361,11 +4911,6 @@
       <c r="R32" t="n">
         <v>0.02115690348914575</v>
       </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5378,22 +4923,12 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR32" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="n">
         <v>0</v>
-      </c>
-      <c r="AU32" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
@@ -5514,11 +5049,6 @@
       <c r="R33" t="n">
         <v>0.0169255227913166</v>
       </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5531,22 +5061,12 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR33" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="n">
         <v>0</v>
-      </c>
-      <c r="AU33" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
@@ -5667,11 +5187,6 @@
       <c r="R34" t="n">
         <v>0.0169255227913166</v>
       </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5684,22 +5199,12 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR34" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="n">
         <v>0</v>
-      </c>
-      <c r="AU34" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
@@ -5820,11 +5325,6 @@
       <c r="R35" t="n">
         <v>0.008462761395658299</v>
       </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5837,22 +5337,12 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR35" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="n">
         <v>0</v>
-      </c>
-      <c r="AU35" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
@@ -5973,11 +5463,6 @@
       <c r="R36" t="n">
         <v>0.02115690348914575</v>
       </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5990,22 +5475,12 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR36" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="n">
         <v>0</v>
-      </c>
-      <c r="AU36" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
@@ -6126,11 +5601,6 @@
       <c r="R37" t="n">
         <v>0.004226666844186674</v>
       </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6143,22 +5613,12 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR37" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="n">
         <v>0</v>
-      </c>
-      <c r="AU37" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
@@ -6279,11 +5739,6 @@
       <c r="R38" t="n">
         <v>0.02113333422093337</v>
       </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6296,22 +5751,12 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR38" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="n">
         <v>0</v>
-      </c>
-      <c r="AU38" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
@@ -6432,11 +5877,6 @@
       <c r="R39" t="n">
         <v>0.01268000053256002</v>
       </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6449,22 +5889,12 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR39" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="n">
         <v>0</v>
-      </c>
-      <c r="AU39" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV39" t="inlineStr">
         <is>
@@ -6585,11 +6015,6 @@
       <c r="R40" t="n">
         <v>0.03381333475349339</v>
       </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6602,22 +6027,12 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR40" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="n">
         <v>0</v>
-      </c>
-      <c r="AU40" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV40" t="inlineStr">
         <is>
@@ -6738,11 +6153,6 @@
       <c r="R41" t="n">
         <v>0.02113333422093337</v>
       </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6755,22 +6165,12 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR41" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="n">
         <v>0</v>
-      </c>
-      <c r="AU41" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV41" t="inlineStr">
         <is>
@@ -6891,11 +6291,6 @@
       <c r="R42" t="n">
         <v>0.004226666844186674</v>
       </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6908,22 +6303,12 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR42" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="n">
         <v>0</v>
-      </c>
-      <c r="AU42" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
@@ -7044,11 +6429,6 @@
       <c r="R43" t="n">
         <v>0.02113333422093337</v>
       </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7061,22 +6441,12 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR43" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="n">
         <v>0</v>
-      </c>
-      <c r="AU43" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
@@ -7197,11 +6567,6 @@
       <c r="R44" t="n">
         <v>0.03804000159768007</v>
       </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7214,22 +6579,12 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR44" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="n">
         <v>0</v>
-      </c>
-      <c r="AU44" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
@@ -7350,11 +6705,6 @@
       <c r="R45" t="n">
         <v>0.03381333475349339</v>
       </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7367,22 +6717,12 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR45" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="n">
         <v>0</v>
-      </c>
-      <c r="AU45" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
@@ -7503,11 +6843,6 @@
       <c r="R46" t="n">
         <v>0.02958666790930672</v>
       </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7520,22 +6855,12 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR46" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="n">
         <v>0</v>
-      </c>
-      <c r="AU46" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV46" t="inlineStr">
         <is>
@@ -7656,11 +6981,6 @@
       <c r="R47" t="n">
         <v>0.008453333688373348</v>
       </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7673,22 +6993,12 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR47" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="n">
         <v>0</v>
-      </c>
-      <c r="AU47" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV47" t="inlineStr">
         <is>
@@ -7809,11 +7119,6 @@
       <c r="R48" t="n">
         <v>0.008453333688373348</v>
       </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7826,22 +7131,12 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR48" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="n">
         <v>0</v>
-      </c>
-      <c r="AU48" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV48" t="inlineStr">
         <is>
@@ -7962,11 +7257,6 @@
       <c r="R49" t="n">
         <v>0.03379214976680777</v>
       </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7979,22 +7269,12 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR49" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="n">
         <v>0</v>
-      </c>
-      <c r="AU49" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
@@ -8115,11 +7395,6 @@
       <c r="R50" t="n">
         <v>0.02534411232510583</v>
       </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8132,22 +7407,12 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR50" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="n">
         <v>0</v>
-      </c>
-      <c r="AU50" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV50" t="inlineStr">
         <is>
@@ -8268,11 +7533,6 @@
       <c r="R51" t="n">
         <v>0.02534411232510583</v>
       </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8285,22 +7545,12 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR51" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="n">
         <v>0</v>
-      </c>
-      <c r="AU51" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV51" t="inlineStr">
         <is>
@@ -8421,11 +7671,6 @@
       <c r="R52" t="n">
         <v>0.01267205616255291</v>
       </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8438,22 +7683,12 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR52" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="n">
         <v>0</v>
-      </c>
-      <c r="AU52" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV52" t="inlineStr">
         <is>
@@ -8574,11 +7809,6 @@
       <c r="R53" t="n">
         <v>0.01689607488340389</v>
       </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8591,22 +7821,12 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR53" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="n">
         <v>0</v>
-      </c>
-      <c r="AU53" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
@@ -8727,11 +7947,6 @@
       <c r="R54" t="n">
         <v>0.01267205616255291</v>
       </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8744,22 +7959,12 @@
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR54" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="n">
         <v>0</v>
-      </c>
-      <c r="AU54" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV54" t="inlineStr">
         <is>
@@ -8880,11 +8085,6 @@
       <c r="R55" t="n">
         <v>0.03379214976680777</v>
       </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8897,22 +8097,12 @@
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR55" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="n">
         <v>0</v>
-      </c>
-      <c r="AU55" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
@@ -9033,11 +8223,6 @@
       <c r="R56" t="n">
         <v>0.02956813104595679</v>
       </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9050,22 +8235,12 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR56" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="n">
         <v>0</v>
-      </c>
-      <c r="AU56" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
@@ -9186,11 +8361,6 @@
       <c r="R57" t="n">
         <v>0.02112009360425485</v>
       </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9203,22 +8373,12 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR57" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="n">
         <v>0</v>
-      </c>
-      <c r="AU57" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
@@ -9339,11 +8499,6 @@
       <c r="R58" t="n">
         <v>0.01267205616255291</v>
       </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9356,22 +8511,12 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR58" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="n">
         <v>0</v>
-      </c>
-      <c r="AU58" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV58" t="inlineStr">
         <is>
@@ -9492,11 +8637,6 @@
       <c r="R59" t="n">
         <v>0.01689607488340389</v>
       </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9509,22 +8649,12 @@
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR59" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="n">
         <v>0</v>
-      </c>
-      <c r="AU59" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
@@ -9645,11 +8775,6 @@
       <c r="R60" t="n">
         <v>0.008448037441701943</v>
       </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9662,22 +8787,12 @@
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR60" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="n">
         <v>0</v>
-      </c>
-      <c r="AU60" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV60" t="inlineStr">
         <is>
